--- a/Doc/pw19_2_data_dictionary.xlsx
+++ b/Doc/pw19_2_data_dictionary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RepoGithub\PW19_2\Pw19_2\Doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RepoGithub\Pw19_2\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF57B97A-239F-4BA4-9F7F-100DC114A6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790D6969-02B6-474C-BEF1-37C10D058223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{79D01E88-2FDA-4818-B7A4-54CE991A2FE5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="228">
   <si>
     <t>Tabella</t>
   </si>
@@ -68,9 +68,6 @@
     <t>id_azienda</t>
   </si>
   <si>
-    <t>SI</t>
-  </si>
-  <si>
     <t>ragione_sociale</t>
   </si>
   <si>
@@ -191,18 +188,12 @@
     <t>ATTIVO</t>
   </si>
   <si>
-    <t>ATTIVO, IN_MANUTENZIONE, DISMESSO</t>
-  </si>
-  <si>
     <t>ambiente</t>
   </si>
   <si>
     <t>PRODUZIONE</t>
   </si>
   <si>
-    <t>PRODUZIONE, TEST, SVILUPPO</t>
-  </si>
-  <si>
     <t>ubicazione</t>
   </si>
   <si>
@@ -254,18 +245,12 @@
     <t>severita</t>
   </si>
   <si>
-    <t>BASSA, MEDIA, ALTA, CRITICA</t>
-  </si>
-  <si>
     <t>data_rilevazione</t>
   </si>
   <si>
     <t>APERTA</t>
   </si>
   <si>
-    <t>APERTA, IN_GESTIONE, RISOLTA</t>
-  </si>
-  <si>
     <t>controlli_compliance</t>
   </si>
   <si>
@@ -293,9 +278,6 @@
     <t>NON_VALUTATO</t>
   </si>
   <si>
-    <t>NON_VALUTATO, NON_CONFORME, PARZIALE, CONFORME</t>
-  </si>
-  <si>
     <t>data_verifica</t>
   </si>
   <si>
@@ -317,9 +299,6 @@
     <t>APERTO</t>
   </si>
   <si>
-    <t>APERTO, IN_GESTIONE, RISOLTO, CHIUSO</t>
-  </si>
-  <si>
     <t>data_apertura</t>
   </si>
   <si>
@@ -356,18 +335,12 @@
     <t>tipo_notifica</t>
   </si>
   <si>
-    <t>PREALLARME_24H, NOTIFICA_72H, RELAZIONE_FINALE, AGGIORNAMENTO</t>
-  </si>
-  <si>
     <t>stato_notifica</t>
   </si>
   <si>
     <t>DA_INVIARE</t>
   </si>
   <si>
-    <t>DA_INVIARE, INVIATA, ACCETTATA, RESPINTA, NON_NECESSARIA</t>
-  </si>
-  <si>
     <t>data_invio</t>
   </si>
   <si>
@@ -389,9 +362,6 @@
     <t>azione</t>
   </si>
   <si>
-    <t>INSERT, UPDATE, DELETE</t>
-  </si>
-  <si>
     <t>utente_db</t>
   </si>
   <si>
@@ -440,9 +410,6 @@
     <t>boolean</t>
   </si>
   <si>
-    <t>test</t>
-  </si>
-  <si>
     <t>varchar(30)</t>
   </si>
   <si>
@@ -461,7 +428,301 @@
     <t>sì</t>
   </si>
   <si>
-    <t>Valori  (campi di tipo enum)</t>
+    <t>Sì</t>
+  </si>
+  <si>
+    <t>Descrizione</t>
+  </si>
+  <si>
+    <t>denominazione dell'azienda</t>
+  </si>
+  <si>
+    <t>partita iva</t>
+  </si>
+  <si>
+    <t>e-mail</t>
+  </si>
+  <si>
+    <t>nome del tipo di asset</t>
+  </si>
+  <si>
+    <t>id del ruolo</t>
+  </si>
+  <si>
+    <t>id del fornitore</t>
+  </si>
+  <si>
+    <t>id del servizio</t>
+  </si>
+  <si>
+    <t>id del tipo di asset</t>
+  </si>
+  <si>
+    <t>id dell'azienda</t>
+  </si>
+  <si>
+    <t>nome del ruolo</t>
+  </si>
+  <si>
+    <t>nome del servizio</t>
+  </si>
+  <si>
+    <t>id del livello di criticità</t>
+  </si>
+  <si>
+    <t>livello di criticità</t>
+  </si>
+  <si>
+    <t>id che identifica l'azienda</t>
+  </si>
+  <si>
+    <t>nome del referente</t>
+  </si>
+  <si>
+    <t>cognome del referente</t>
+  </si>
+  <si>
+    <t>telefono del referente</t>
+  </si>
+  <si>
+    <t>e-mail del referente</t>
+  </si>
+  <si>
+    <t>id della persona</t>
+  </si>
+  <si>
+    <t>nome del dipendente</t>
+  </si>
+  <si>
+    <t>telefono del dipendente</t>
+  </si>
+  <si>
+    <t>cognome del dipendente</t>
+  </si>
+  <si>
+    <t>e-mail del dipendente</t>
+  </si>
+  <si>
+    <t>id del contratto</t>
+  </si>
+  <si>
+    <t>descrizione del servizio</t>
+  </si>
+  <si>
+    <t>id che identifica il fornitore</t>
+  </si>
+  <si>
+    <t>id che identifica il servizio</t>
+  </si>
+  <si>
+    <t>numero che identifica il contratto</t>
+  </si>
+  <si>
+    <t>data inizio del contratto</t>
+  </si>
+  <si>
+    <t>data scadenza del contratto</t>
+  </si>
+  <si>
+    <t>valore di SLA previsto dal contratto</t>
+  </si>
+  <si>
+    <t>disponibilità del servizio garantita</t>
+  </si>
+  <si>
+    <t>note aggiuntive</t>
+  </si>
+  <si>
+    <t>id dell'asset</t>
+  </si>
+  <si>
+    <t>nome dell'asset</t>
+  </si>
+  <si>
+    <t>descrizione dell'asset</t>
+  </si>
+  <si>
+    <t>versione dell'asset</t>
+  </si>
+  <si>
+    <t>id che identifica il tipo di asset</t>
+  </si>
+  <si>
+    <t>id che identifica il contratto</t>
+  </si>
+  <si>
+    <t>id che identifica il livello di criticità</t>
+  </si>
+  <si>
+    <t>stato corrente</t>
+  </si>
+  <si>
+    <t>ambiente di utilizzo</t>
+  </si>
+  <si>
+    <t>localizzazione dell'asset</t>
+  </si>
+  <si>
+    <t>seriale dell'asset</t>
+  </si>
+  <si>
+    <t>sistema operativo dell'asset</t>
+  </si>
+  <si>
+    <t>data di acquisto dell'asset</t>
+  </si>
+  <si>
+    <t>data di dismissione dell'asset</t>
+  </si>
+  <si>
+    <t>stato del backup</t>
+  </si>
+  <si>
+    <t>stato della cifratura</t>
+  </si>
+  <si>
+    <t>id della dipendenza tra asset e servizio</t>
+  </si>
+  <si>
+    <t>id che identifica l'asset</t>
+  </si>
+  <si>
+    <t>id che identifica il responsabile</t>
+  </si>
+  <si>
+    <t>id che identifica il dipendente</t>
+  </si>
+  <si>
+    <t>id che identifica il ruolo</t>
+  </si>
+  <si>
+    <t>id che identifica la vulnerabilità</t>
+  </si>
+  <si>
+    <t>CVE associato alla vulnerabilità</t>
+  </si>
+  <si>
+    <t>descrizione della vulnerabilità</t>
+  </si>
+  <si>
+    <t>livello di severità</t>
+  </si>
+  <si>
+    <t>data in cui è stata rilevata la vulnerabilità</t>
+  </si>
+  <si>
+    <t>stato della vulnerabilità</t>
+  </si>
+  <si>
+    <t>id del controllo</t>
+  </si>
+  <si>
+    <t>nome del controllo</t>
+  </si>
+  <si>
+    <t>riferimento normativo del controllo</t>
+  </si>
+  <si>
+    <t>categoria del controllo</t>
+  </si>
+  <si>
+    <t>descrizione del controllo</t>
+  </si>
+  <si>
+    <t>id della valutazione di compliance</t>
+  </si>
+  <si>
+    <t>id che identifica il controllo</t>
+  </si>
+  <si>
+    <t>esito della verifica</t>
+  </si>
+  <si>
+    <t>data della verifica</t>
+  </si>
+  <si>
+    <t>scostamento rispetto al target</t>
+  </si>
+  <si>
+    <t>azione correttiva</t>
+  </si>
+  <si>
+    <t>id dell'incidente</t>
+  </si>
+  <si>
+    <t>titolo dell'incidente</t>
+  </si>
+  <si>
+    <t>descrizione dell'incidente</t>
+  </si>
+  <si>
+    <t>causa dell'incidente</t>
+  </si>
+  <si>
+    <t>stato dell'incidente</t>
+  </si>
+  <si>
+    <t>data di apertura del caso</t>
+  </si>
+  <si>
+    <t>data di chiusura del caso</t>
+  </si>
+  <si>
+    <t>indica se l'incidente richiede notifica alle autorità</t>
+  </si>
+  <si>
+    <t>soluzione adottata per la gestione del caso</t>
+  </si>
+  <si>
+    <t>id che identifica incidente e asset</t>
+  </si>
+  <si>
+    <t>id che identifica l'incidente</t>
+  </si>
+  <si>
+    <t>id che identifica la notifica dell'incidente</t>
+  </si>
+  <si>
+    <t>destinatario della notifica</t>
+  </si>
+  <si>
+    <t>riferimento normativo della notifica</t>
+  </si>
+  <si>
+    <t>tipologia di notifica</t>
+  </si>
+  <si>
+    <t>stato della notifica</t>
+  </si>
+  <si>
+    <t>data entro cui effettuare la notifica</t>
+  </si>
+  <si>
+    <t>data di invio</t>
+  </si>
+  <si>
+    <t>id del log</t>
+  </si>
+  <si>
+    <t>data e ora del rilevamento</t>
+  </si>
+  <si>
+    <t>la tabella interessata</t>
+  </si>
+  <si>
+    <t>il record interessato dall'operazione</t>
+  </si>
+  <si>
+    <t>operazione eseguita</t>
+  </si>
+  <si>
+    <t>utente che ha eseguito l'operazione</t>
+  </si>
+  <si>
+    <t>valore del record prima dell'operazione</t>
+  </si>
+  <si>
+    <t>valore del record dopo l'operazione</t>
   </si>
 </sst>
 </file>
@@ -816,7 +1077,7 @@
     <tableColumn id="8" xr3:uid="{D07FA0B9-761C-45F8-A70A-10AC7FCD3581}" name="FK" dataDxfId="3"/>
     <tableColumn id="9" xr3:uid="{248D5726-8BC1-4953-B8BC-D06550A87F61}" name="Tabella riferimento FK" dataDxfId="2"/>
     <tableColumn id="11" xr3:uid="{6D498648-5A37-41F5-8DA7-1096B6EAE3C8}" name="Auto increment" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{ED56F25A-F96A-4209-982F-D62FEF19EC8E}" name="Valori  (campi di tipo enum)" dataDxfId="0"/>
+    <tableColumn id="12" xr3:uid="{ED56F25A-F96A-4209-982F-D62FEF19EC8E}" name="Descrizione" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1155,12 +1416,12 @@
     <col min="8" max="8" width="3.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="25.42578125" customWidth="1"/>
     <col min="10" max="10" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="81.28515625" customWidth="1"/>
+    <col min="11" max="11" width="81.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18.75">
       <c r="A1" s="7" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.75" thickBot="1">
@@ -1177,10 +1438,10 @@
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>4</v>
@@ -1189,13 +1450,13 @@
         <v>5</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
@@ -1209,10 +1470,10 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
@@ -1221,9 +1482,11 @@
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="6" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A6" s="2" t="s">
@@ -1233,20 +1496,22 @@
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
+      <c r="K6" s="2" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="7" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A7" s="2" t="s">
@@ -1256,20 +1521,22 @@
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
+      <c r="K7" s="2" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="8" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A8" s="2" t="s">
@@ -1279,20 +1546,22 @@
         <v>4</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
+      <c r="K8" s="2" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="9" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A9" s="2" t="s">
@@ -1302,20 +1571,22 @@
         <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
+      <c r="K9" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="10" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A10" s="3"/>
@@ -1332,19 +1603,19 @@
     </row>
     <row r="11" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A11" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
@@ -1353,32 +1624,36 @@
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="12" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A12" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
+      <c r="K12" s="2" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="13" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A13" s="3"/>
@@ -1395,19 +1670,19 @@
     </row>
     <row r="14" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="2">
         <v>1</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
@@ -1416,32 +1691,36 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K14" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="15" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" s="2">
         <v>2</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
+      <c r="K15" s="2" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="16" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A16" s="3"/>
@@ -1458,19 +1737,19 @@
     </row>
     <row r="17" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A17" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" s="2">
         <v>1</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
@@ -1479,32 +1758,36 @@
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K17" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="18" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A18" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B18" s="2">
         <v>2</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
+      <c r="K18" s="2" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="19" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A19" s="3"/>
@@ -1521,19 +1804,19 @@
     </row>
     <row r="20" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A20" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" s="2">
         <v>1</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
@@ -1542,13 +1825,15 @@
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K20" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="21" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A21" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B21" s="2">
         <v>2</v>
@@ -1557,10 +1842,10 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -1571,99 +1856,109 @@
         <v>7</v>
       </c>
       <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
+      <c r="K21" s="2" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="22" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A22" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" s="5">
         <v>3</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
+      <c r="K22" s="5" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="23" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A23" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" s="2">
         <v>4</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
+      <c r="K23" s="2" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="24" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A24" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="6">
         <v>5</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
+      <c r="K24" s="6" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="25" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A25" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B25" s="2">
         <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
+      <c r="K25" s="2" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="26" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A26" s="3"/>
@@ -1680,19 +1975,19 @@
     </row>
     <row r="27" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A27" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B27" s="2">
         <v>1</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
@@ -1701,13 +1996,15 @@
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K27" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="28" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A28" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B28" s="2">
         <v>2</v>
@@ -1716,10 +2013,10 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -1730,99 +2027,109 @@
         <v>7</v>
       </c>
       <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
+      <c r="K28" s="2" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="29" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A29" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" s="2">
         <v>3</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
+      <c r="K29" s="2" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="30" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A30" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="2">
         <v>4</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
+      <c r="K30" s="2" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="31" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A31" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B31" s="2">
         <v>5</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
+      <c r="K31" s="2" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="32" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A32" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B32" s="2">
         <v>6</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
+      <c r="K32" s="2" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="33" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A33" s="3"/>
@@ -1839,19 +2146,19 @@
     </row>
     <row r="34" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A34" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="2">
         <v>1</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2" t="s">
@@ -1860,13 +2167,15 @@
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K34" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="35" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A35" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B35" s="2">
         <v>2</v>
@@ -1875,10 +2184,10 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -1889,53 +2198,59 @@
         <v>7</v>
       </c>
       <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
+      <c r="K35" s="2" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="36" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A36" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B36" s="2">
         <v>3</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
+      <c r="K36" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="37" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A37" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B37" s="2">
         <v>4</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D37" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
+      <c r="K37" s="2" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="38" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A38" s="3"/>
@@ -1952,19 +2267,19 @@
     </row>
     <row r="39" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A39" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B39" s="2">
         <v>1</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
@@ -1973,13 +2288,15 @@
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K39" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="40" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A40" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B40" s="2">
         <v>2</v>
@@ -1988,10 +2305,10 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -2002,23 +2319,25 @@
         <v>7</v>
       </c>
       <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
+      <c r="K40" s="2" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="41" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A41" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B41" s="2">
         <v>3</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -2026,26 +2345,28 @@
         <v>5</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
+      <c r="K41" s="2" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="42" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A42" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B42" s="2">
         <v>4</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -2053,148 +2374,162 @@
         <v>5</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J42" s="2"/>
-      <c r="K42" s="2"/>
+      <c r="K42" s="2" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="43" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A43" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B43" s="2">
         <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
+      <c r="K43" s="2" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="44" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A44" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B44" s="2">
         <v>6</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
+      <c r="K44" s="2" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="45" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A45" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B45" s="2">
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
+      <c r="K45" s="2" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="46" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A46" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B46" s="2">
         <v>8</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
+      <c r="K46" s="2" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="47" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A47" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B47" s="2">
         <v>9</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
+      <c r="K47" s="2" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="48" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A48" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B48" s="2">
         <v>10</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D48" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
+      <c r="K48" s="2" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="49" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A49" s="3"/>
@@ -2211,19 +2546,19 @@
     </row>
     <row r="50" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A50" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B50" s="2">
         <v>1</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2" t="s">
@@ -2232,13 +2567,15 @@
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K50" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="51" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A51" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B51" s="2">
         <v>2</v>
@@ -2247,10 +2584,10 @@
         <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
@@ -2261,69 +2598,75 @@
         <v>7</v>
       </c>
       <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
+      <c r="K51" s="2" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="52" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A52" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B52" s="2">
         <v>3</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
+      <c r="K52" s="2" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="53" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A53" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B53" s="2">
         <v>4</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D53" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
+      <c r="K53" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="54" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A54" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B54" s="2">
         <v>5</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
@@ -2331,26 +2674,28 @@
         <v>5</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
+      <c r="K54" s="2" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="55" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A55" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B55" s="2">
         <v>6</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
@@ -2358,26 +2703,28 @@
         <v>5</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
+      <c r="K55" s="2" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="56" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A56" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B56" s="2">
         <v>7</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
@@ -2385,275 +2732,295 @@
         <v>5</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J56" s="2"/>
-      <c r="K56" s="2"/>
+      <c r="K56" s="2" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="57" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A57" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B57" s="2">
         <v>8</v>
       </c>
       <c r="C57" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2" t="s">
-        <v>50</v>
+        <v>171</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A58" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B58" s="2">
         <v>9</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2" t="s">
-        <v>53</v>
+        <v>172</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A59" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B59" s="2">
         <v>10</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
+      <c r="K59" s="2" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="60" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A60" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B60" s="2">
         <v>11</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
-      <c r="K60" s="2"/>
+      <c r="K60" s="2" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="61" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A61" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B61" s="2">
         <v>12</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
-      <c r="K61" s="2"/>
+      <c r="K61" s="2" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="62" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A62" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B62" s="2">
         <v>13</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
-      <c r="K62" s="2"/>
+      <c r="K62" s="2" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="63" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A63" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B63" s="2">
         <v>14</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
-      <c r="K63" s="2"/>
+      <c r="K63" s="2" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="64" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A64" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B64" s="2">
         <v>15</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
-      <c r="K64" s="2"/>
+      <c r="K64" s="2" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="65" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A65" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B65" s="2">
         <v>16</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
-      <c r="K65" s="2"/>
+      <c r="K65" s="2" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="66" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A66" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B66" s="2">
         <v>17</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
+      <c r="K66" s="2" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="67" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A67" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B67" s="2">
         <v>18</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
-      <c r="K67" s="2"/>
+      <c r="K67" s="2" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="68" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A68" s="3"/>
@@ -2670,19 +3037,19 @@
     </row>
     <row r="69" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A69" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B69" s="2">
         <v>1</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2" t="s">
@@ -2691,25 +3058,27 @@
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
       <c r="J69" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K69" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="70" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A70" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B70" s="2">
         <v>2</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
@@ -2717,26 +3086,28 @@
         <v>5</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J70" s="2"/>
-      <c r="K70" s="2"/>
+      <c r="K70" s="2" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="71" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A71" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B71" s="2">
         <v>3</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
@@ -2744,10 +3115,12 @@
         <v>5</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J71" s="2"/>
-      <c r="K71" s="2"/>
+      <c r="K71" s="2" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="72" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A72" s="3"/>
@@ -2764,19 +3137,19 @@
     </row>
     <row r="73" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A73" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B73" s="2">
         <v>1</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2" t="s">
@@ -2785,25 +3158,27 @@
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
       <c r="J73" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K73" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="74" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A74" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B74" s="2">
         <v>2</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
@@ -2811,26 +3186,28 @@
         <v>5</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J74" s="2"/>
-      <c r="K74" s="2"/>
+      <c r="K74" s="2" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="75" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A75" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B75" s="2">
         <v>3</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
@@ -2838,26 +3215,28 @@
         <v>5</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J75" s="2"/>
-      <c r="K75" s="2"/>
+      <c r="K75" s="2" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="76" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A76" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B76" s="2">
         <v>4</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
@@ -2865,10 +3244,12 @@
         <v>5</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J76" s="2"/>
-      <c r="K76" s="2"/>
+      <c r="K76" s="2" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="77" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A77" s="3"/>
@@ -2885,19 +3266,19 @@
     </row>
     <row r="78" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A78" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B78" s="2">
         <v>1</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2" t="s">
@@ -2906,25 +3287,27 @@
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
       <c r="J78" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K78" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="79" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A79" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B79" s="2">
         <v>2</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -2932,72 +3315,78 @@
         <v>5</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J79" s="2"/>
-      <c r="K79" s="2"/>
+      <c r="K79" s="2" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="80" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A80" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B80" s="2">
         <v>3</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
       <c r="J80" s="2"/>
-      <c r="K80" s="2"/>
+      <c r="K80" s="2" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="81" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A81" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B81" s="2">
         <v>4</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
       <c r="J81" s="2"/>
-      <c r="K81" s="2"/>
+      <c r="K81" s="2" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="82" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A82" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B82" s="2">
         <v>5</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
@@ -3005,57 +3394,59 @@
       <c r="I82" s="2"/>
       <c r="J82" s="2"/>
       <c r="K82" s="2" t="s">
-        <v>71</v>
+        <v>188</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A83" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B83" s="2">
         <v>6</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
       <c r="J83" s="2"/>
-      <c r="K83" s="2"/>
+      <c r="K83" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="84" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A84" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B84" s="2">
         <v>7</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
       <c r="J84" s="2"/>
       <c r="K84" s="2" t="s">
-        <v>74</v>
+        <v>190</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
@@ -3073,19 +3464,19 @@
     </row>
     <row r="86" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A86" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B86" s="2">
         <v>1</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" s="2" t="s">
@@ -3094,101 +3485,111 @@
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
       <c r="J86" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K86" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="87" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A87" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B87" s="2">
         <v>2</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
       <c r="J87" s="2"/>
-      <c r="K87" s="2"/>
+      <c r="K87" s="2" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="88" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A88" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B88" s="2">
         <v>3</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
       <c r="I88" s="2"/>
       <c r="J88" s="2"/>
-      <c r="K88" s="2"/>
+      <c r="K88" s="2" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="89" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A89" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B89" s="2">
         <v>4</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
       <c r="I89" s="2"/>
       <c r="J89" s="2"/>
-      <c r="K89" s="2"/>
+      <c r="K89" s="2" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="90" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A90" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B90" s="2">
         <v>5</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D90" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E90" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
-      <c r="K90" s="2"/>
+      <c r="K90" s="2" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="91" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A91" s="3"/>
@@ -3205,19 +3606,19 @@
     </row>
     <row r="92" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A92" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B92" s="2">
         <v>1</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F92" s="2"/>
       <c r="G92" s="2" t="s">
@@ -3226,13 +3627,15 @@
       <c r="H92" s="2"/>
       <c r="I92" s="2"/>
       <c r="J92" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K92" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="K92" s="2" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="93" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A93" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B93" s="2">
         <v>2</v>
@@ -3241,10 +3644,10 @@
         <v>8</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
@@ -3255,23 +3658,25 @@
         <v>7</v>
       </c>
       <c r="J93" s="2"/>
-      <c r="K93" s="2"/>
+      <c r="K93" s="2" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="94" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A94" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B94" s="2">
         <v>3</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
@@ -3279,129 +3684,139 @@
         <v>5</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="J94" s="2"/>
-      <c r="K94" s="2"/>
+      <c r="K94" s="2" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="95" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A95" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B95" s="2">
         <v>4</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
       <c r="J95" s="2"/>
       <c r="K95" s="2" t="s">
-        <v>84</v>
+        <v>198</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A96" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B96" s="2">
         <v>5</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
-      <c r="K96" s="2"/>
+      <c r="K96" s="2" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="97" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A97" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B97" s="2">
         <v>6</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D97" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E97" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
       <c r="J97" s="2"/>
-      <c r="K97" s="2"/>
+      <c r="K97" s="2" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="98" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A98" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B98" s="2">
         <v>7</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D98" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E98" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
       <c r="I98" s="2"/>
       <c r="J98" s="2"/>
-      <c r="K98" s="2"/>
+      <c r="K98" s="2" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="99" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A99" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B99" s="2">
         <v>8</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D99" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E99" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
       <c r="J99" s="2"/>
-      <c r="K99" s="2"/>
+      <c r="K99" s="2" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="100" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A100" s="3"/>
@@ -3418,19 +3833,19 @@
     </row>
     <row r="101" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A101" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B101" s="2">
         <v>1</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F101" s="2"/>
       <c r="G101" s="2" t="s">
@@ -3439,13 +3854,15 @@
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
       <c r="J101" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K101" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="K101" s="2" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="102" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A102" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B102" s="2">
         <v>2</v>
@@ -3454,10 +3871,10 @@
         <v>8</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
@@ -3468,69 +3885,75 @@
         <v>7</v>
       </c>
       <c r="J102" s="2"/>
-      <c r="K102" s="2"/>
+      <c r="K102" s="2" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="103" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A103" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B103" s="2">
         <v>3</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
       <c r="I103" s="2"/>
       <c r="J103" s="2"/>
-      <c r="K103" s="2"/>
+      <c r="K103" s="2" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="104" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A104" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B104" s="2">
         <v>4</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
       <c r="I104" s="2"/>
       <c r="J104" s="2"/>
-      <c r="K104" s="2"/>
+      <c r="K104" s="2" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="105" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A105" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B105" s="2">
         <v>5</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
@@ -3538,177 +3961,189 @@
       <c r="I105" s="2"/>
       <c r="J105" s="2"/>
       <c r="K105" s="2" t="s">
-        <v>71</v>
+        <v>188</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A106" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B106" s="2">
         <v>6</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
       <c r="I106" s="2"/>
       <c r="J106" s="2"/>
       <c r="K106" s="2" t="s">
-        <v>92</v>
+        <v>206</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A107" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B107" s="2">
         <v>7</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
       <c r="I107" s="2"/>
       <c r="J107" s="2"/>
-      <c r="K107" s="2"/>
+      <c r="K107" s="2" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="108" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A108" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B108" s="2">
         <v>8</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
       <c r="I108" s="2"/>
       <c r="J108" s="2"/>
-      <c r="K108" s="2"/>
+      <c r="K108" s="2" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="109" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A109" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B109" s="2">
         <v>9</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
       <c r="I109" s="2"/>
       <c r="J109" s="2"/>
-      <c r="K109" s="2"/>
+      <c r="K109" s="2" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="110" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A110" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B110" s="2">
         <v>10</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D110" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E110" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
       <c r="I110" s="2"/>
       <c r="J110" s="2"/>
-      <c r="K110" s="2"/>
+      <c r="K110" s="2" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="111" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A111" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B111" s="2">
         <v>11</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D111" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E111" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
       <c r="I111" s="2"/>
       <c r="J111" s="2"/>
-      <c r="K111" s="2"/>
+      <c r="K111" s="2" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="112" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A112" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B112" s="2">
         <v>12</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D112" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E112" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
       <c r="I112" s="2"/>
       <c r="J112" s="2"/>
-      <c r="K112" s="2"/>
+      <c r="K112" s="2" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="113" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A113" s="3"/>
@@ -3725,19 +4160,19 @@
     </row>
     <row r="114" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A114" s="2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B114" s="2">
         <v>1</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F114" s="2"/>
       <c r="G114" s="2" t="s">
@@ -3745,24 +4180,28 @@
       </c>
       <c r="H114" s="2"/>
       <c r="I114" s="2"/>
-      <c r="J114" s="2"/>
-      <c r="K114" s="2"/>
+      <c r="J114" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="K114" s="2" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="115" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A115" s="2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B115" s="2">
         <v>2</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
@@ -3770,26 +4209,28 @@
         <v>5</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J115" s="2"/>
-      <c r="K115" s="2"/>
+      <c r="K115" s="2" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="116" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A116" s="2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B116" s="2">
         <v>3</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
@@ -3797,10 +4238,12 @@
         <v>5</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J116" s="2"/>
-      <c r="K116" s="2"/>
+      <c r="K116" s="2" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="117" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A117" s="3"/>
@@ -3817,19 +4260,19 @@
     </row>
     <row r="118" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A118" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B118" s="2">
         <v>1</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F118" s="2"/>
       <c r="G118" s="2" t="s">
@@ -3838,25 +4281,27 @@
       <c r="H118" s="2"/>
       <c r="I118" s="2"/>
       <c r="J118" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K118" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="K118" s="2" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="119" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A119" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B119" s="2">
         <v>2</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
@@ -3864,72 +4309,78 @@
         <v>5</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J119" s="2"/>
-      <c r="K119" s="2"/>
+      <c r="K119" s="2" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="120" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A120" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B120" s="2">
         <v>3</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
       <c r="I120" s="2"/>
       <c r="J120" s="2"/>
-      <c r="K120" s="2"/>
+      <c r="K120" s="2" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="121" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A121" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B121" s="2">
         <v>4</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
       <c r="I121" s="2"/>
       <c r="J121" s="2"/>
-      <c r="K121" s="2"/>
+      <c r="K121" s="2" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="122" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A122" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B122" s="2">
         <v>5</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
@@ -3937,104 +4388,110 @@
       <c r="I122" s="2"/>
       <c r="J122" s="2"/>
       <c r="K122" s="2" t="s">
-        <v>105</v>
+        <v>216</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A123" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B123" s="2">
         <v>6</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
       <c r="I123" s="2"/>
       <c r="J123" s="2"/>
       <c r="K123" s="2" t="s">
-        <v>108</v>
+        <v>217</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A124" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B124" s="2">
         <v>7</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
       <c r="I124" s="2"/>
       <c r="J124" s="2"/>
-      <c r="K124" s="2"/>
+      <c r="K124" s="2" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="125" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A125" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B125" s="2">
         <v>8</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
       <c r="I125" s="2"/>
       <c r="J125" s="2"/>
-      <c r="K125" s="2"/>
+      <c r="K125" s="2" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="126" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A126" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B126" s="2">
         <v>9</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D126" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E126" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
       <c r="I126" s="2"/>
       <c r="J126" s="2"/>
-      <c r="K126" s="2"/>
+      <c r="K126" s="2" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="127" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A127" s="3"/>
@@ -4051,19 +4508,19 @@
     </row>
     <row r="128" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A128" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B128" s="2">
         <v>1</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F128" s="2"/>
       <c r="G128" s="2" t="s">
@@ -4072,96 +4529,104 @@
       <c r="H128" s="2"/>
       <c r="I128" s="2"/>
       <c r="J128" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K128" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="K128" s="2" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="129" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A129" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B129" s="2">
         <v>2</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
       <c r="I129" s="2"/>
       <c r="J129" s="2"/>
-      <c r="K129" s="2"/>
+      <c r="K129" s="2" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="130" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A130" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B130" s="2">
         <v>3</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
       <c r="I130" s="2"/>
       <c r="J130" s="2"/>
-      <c r="K130" s="2"/>
+      <c r="K130" s="2" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="131" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A131" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B131" s="2">
         <v>4</v>
       </c>
       <c r="C131" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D131" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D131" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="E131" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
       <c r="I131" s="2"/>
       <c r="J131" s="2"/>
-      <c r="K131" s="2"/>
+      <c r="K131" s="2" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="132" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A132" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B132" s="2">
         <v>5</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
@@ -4169,77 +4634,83 @@
       <c r="I132" s="2"/>
       <c r="J132" s="2"/>
       <c r="K132" s="2" t="s">
-        <v>116</v>
+        <v>224</v>
       </c>
     </row>
     <row r="133" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A133" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B133" s="2">
         <v>6</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
       <c r="I133" s="2"/>
       <c r="J133" s="2"/>
-      <c r="K133" s="2"/>
+      <c r="K133" s="2" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="134" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A134" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B134" s="2">
         <v>7</v>
       </c>
       <c r="C134" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D134" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D134" s="2" t="s">
+      <c r="E134" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
       <c r="I134" s="2"/>
       <c r="J134" s="2"/>
-      <c r="K134" s="2"/>
+      <c r="K134" s="2" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="135" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A135" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B135" s="2">
         <v>8</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D135" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E135" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
       <c r="I135" s="2"/>
       <c r="J135" s="2"/>
-      <c r="K135" s="2"/>
+      <c r="K135" s="2" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="136" spans="1:11" ht="15.75" thickTop="1"/>
   </sheetData>
